--- a/그린바이오산업_특수분류표.xlsx
+++ b/그린바이오산업_특수분류표.xlsx
@@ -205,7 +205,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대분류 5 · 중분류 17 · 소분류 36   |   작업안 · 국가데이터처 승인 전   |   정의 원문은 소분류 정의서</t>
+          <t xml:space="preserve">대분류 5 · 중분류 17 · 소분류 32   |   작업안 · 국가데이터처 승인 전   |   정의 원문은 소분류 정의서</t>
         </is>
       </c>
     </row>
@@ -246,7 +246,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1">
+    <row r="5" ht="111" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -269,21 +269,21 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">111</t>
+          <t xml:space="preserve">110</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 연구·생산용 자재 제조업</t>
+          <t xml:space="preserve">그린바이오 기자재 제조업</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조 공정에 전용되거나 주로 사용되도록 특화된 배지·배양기질·시약·효소·완충용액·시약키트·유전자 벡터·담체·공정재 등 소모성 자재를 직접 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
+          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조에 전용되거나 주로 사용되도록 특화된 기자재를 직접 제조하는 산업활동을 말한다. 배지·배양기질·시약·효소·완충용액·시약키트·유전자 벡터·담체·공정재 등 소모성 자재, 유전·세포·생물정보 또는 성분·품질·안전을 시험·측정·분석하는 연구·분석장비와 그 전용 부품, 배양·발효·분리·정제·건조·제형 장비와 생물자원의 증식·사육·재배 환경제어 장비 등 생산·공정장비를 포함한다. 자체 제조한 기자재의 판매는 이 산업활동에 포함한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -296,142 +296,142 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 기자재 제조업</t>
+          <t xml:space="preserve">그린바이오 기자재 도매업</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">112</t>
+          <t xml:space="preserve">120</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 연구·분석장비 제조업</t>
+          <t xml:space="preserve">그린바이오 기자재 도매업</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품과 그 생산·제조공정을 대상으로 유전·세포·생물정보 또는 성분·품질·안전을 시험·측정·분석하는 데 전용되거나 주로 사용되도록 특화된 장비와 그 전용 부품을 직접 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="81" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 기자재 공급업</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 기자재 제조업</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생산·공정장비 제조업</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 생산·제조에 사용하는 배양·발효·분리·정제·건조·제형 장비 또는 생물자원의 증식·사육·재배 환경제어 장비로서, 해당 공정의 생물학적 품질·안전 요건에 맞게 전용되거나 주로 사용되도록 특화된 것을 직접 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="111" customHeight="1">
+          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조에 전용되거나 주로 사용되도록 특화된 타사 제조 기자재를 매입하거나 수입하여, 본질적으로 변형하지 않고 사업자·연구기관·생산자에게 재판매하며 해당 품목·매출을 일반 기자재와 분리하는 산업활동을 말한다. 배지·시약·효소·시약키트·담체·공정재 등 소모성 자재, 유전·세포·생물정보와 성분·품질·안전을 시험·측정·분석하는 연구·분석장비, 배양·발효·분리·정제·건조·제형 장비와 생물자원 증식·사육·재배 환경제어 장비 등 생산·공정장비를 포함한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="51" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 종자·종묘 생산업</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생명공학 관련 육종·유전체·선발·편집 기술을 적용하여 식물 품종을 개발하거나 해당 품종의 원원종·원종·모본·부본·보급종·판매용 종자·묘목·묘종·조직배양묘를 생산·증식하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="81" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 기자재 공급업</t>
+          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 기자재 도매업</t>
+          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">120</t>
+          <t xml:space="preserve">212</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 기자재 도매업</t>
+          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조에 전용되거나 주로 사용되도록 특화된 타사 제조 기자재를 매입하거나 수입하여, 본질적으로 변형하지 않고 사업자·연구기관·생산자에게 재판매하며 해당 품목·매출을 일반 기자재와 분리하는 산업활동을 말한다. 배지·시약·효소·시약키트·담체·공정재 등 소모성 자재, 유전·세포·생물정보와 성분·품질·안전을 시험·측정·분석하는 연구·분석장비, 배양·발효·분리·정제·건조·제형 장비와 생물자원 증식·사육·재배 환경제어 장비 등 생산·공정장비를 포함한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+          <t xml:space="preserve">유용성분·기능성 형질의 탐색·선발·개량 또는 생산관리에 생명공학 관련 기술을 적용하거나, 확인된 그린바이오 소재·제품 제조공정의 성분·품질규격 또는 계약에 따라, 그 원료로 사용하는 식물체 또는 수확물을 재배·생산하는 산업활동을 말한다. 노지·시설·수경·식물공장 등 재배방식은 묻지 않으며, 수확물이 실제로 그린바이오 소재·제품의 원료로 공급되는 관계가 확인되어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원 생산업</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 종자·종묘 생산업</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생명공학 관련 육종·유전체·선발·편집 기술을 적용하여 식물 품종을 개발하거나 해당 품종의 원원종·원종·모본·부본·보급종·판매용 종자·묘목·묘종·조직배양묘를 생산·증식하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="81" customHeight="1">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생명공학 관련 기술을 적용해 「곤충산업의 육성 및 지원에 관한 법률」상 곤충, 즉 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 같은 법이 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등)의 계통·품종을 선발·개량하여 종충·종란 등 증식 기반자원을 생산하거나, 식품·사료·방제·소재용 곤충을 증식·사육하는 산업활동을 말한다. 확인된 그린바이오 제조규격에 따른 계약 사육을 포함한다. 번식 기반자원 생산과 산업용 사육은 공급용도 속성으로 구분한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -444,27 +444,27 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식물자원 생산업</t>
+          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">212</t>
+          <t xml:space="preserve">231</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 소재 원료용 식물 생산업</t>
+          <t xml:space="preserve">그린바이오 미생물자원 생산업</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">유용성분·기능성 형질의 탐색·선발·개량 또는 생산관리에 생명공학 관련 기술을 적용하거나, 확인된 그린바이오 소재·제품 제조공정의 성분·품질규격 또는 계약에 따라, 그 원료로 사용하는 식물체 또는 수확물을 재배·생산하는 산업활동을 말한다. 노지·시설·수경·식물공장 등 재배방식은 묻지 않으며, 수확물이 실제로 그린바이오 소재·제품의 원료로 공급되는 관계가 확인되어야 한다.</t>
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물의 종균·스타터·균주 자체를 생명공학 관련 기술로 발굴·제작·배양·증식하여 그린바이오 연구·생산에 공급하는 산업활동을 말한다. 농업·식품·사료·소재 분야에 이용하는 세균·효모·곰팡이·미세조류 등을 포함하며, 그 농업적 가치는 적용 분야와 용도로 확인한다.</t>
         </is>
       </c>
     </row>
@@ -481,179 +481,179 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
+          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">221</t>
+          <t xml:space="preserve">232</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 곤충 종충·품종자원 생산업</t>
+          <t xml:space="preserve">그린바이오 세포·조직자원 생산업</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 기술을 적용해 「곤충산업의 육성 및 지원에 관한 법률」상 곤충, 즉 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 같은 법이 정하는 무척추동물의 계통·품종을 선발·개량하고 종충·종란 등 증식 기반자원을 생산하는 산업활동을 말한다. 천적으로 이용하는 응애류처럼 곤충강에 속하지 않는 무척추동물도 같은 법의 곤충에 해당하면 포함한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 곤충자원 생산업</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 산업용 곤충 사육·생산업</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용된 식품·사료·방제·소재용 곤충(「곤충산업의 육성 및 지원에 관한 법률」상 곤충, 즉 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 같은 법이 정하는 무척추동물)을 증식·사육하거나 확인된 그린바이오 제조규격에 따라 계약 사육하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
+          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 생물기원 천연물의 원천이 되는 육상·해양 생물체에서 유래한 세포·조직·세포주 자원 자체를 생명공학 관련 기술로 제작·배양·증식하여 그린바이오 연구·생산에 공급하는 산업활동을 말한다. 자원의 원천 생물체가 위 관련 분야에 해당함을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="141" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생물농약·생물방제제품 제조업</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">병해충 방제 또는 농작물 생리기능 조절에 사용하는 농약·방제제품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물 또는 생명공학 관련 기술·생물공정을 유효성분이나 방제기능에 직접 이용하여 제조하는 산업활동을 말한다. 살아 있는 미생물 또는 자연계 생성 화합물을 유효성분으로 하는 천연식물보호제도 이러한 생물자원과 연결되고 생명공학 관련 기술·생물공정의 직접 기여가 함께 확인되면 포함한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
+          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">231</t>
+          <t xml:space="preserve">312</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물자원 생산업</t>
+          <t xml:space="preserve">그린바이오 비료 제조업</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 연구·생산에 이용할 종균·스타터·균주 자체를 생명공학 관련 기술로 발굴·제작·배양·증식하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
+          <t xml:space="preserve">미생물·식물·해조류 등 그린바이오 생물자원 또는 발효·효소처리·생물전환 등의 생물공정을 이용하여 식물에 양분을 공급하거나 토양의 물리적·화학적·생물학적 특성을 개선하는 비료를 제조하는 산업활동을 말한다. 유용 미생물, 미생물 배양물·대사산물, 발효 아미노산·유기산 및 생물전환 양분 소재를 이용한 비료를 포함한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원 생산업</t>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물 및 세포·조직자원 생산업</t>
+          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">232</t>
+          <t xml:space="preserve">319</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 세포·조직자원 생산업</t>
+          <t xml:space="preserve">기타 그린바이오 작물재배용 제품 제조업</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 소재·제품의 연구·생산에 이용할 식물·동물·곤충의 세포·조직·세포주 자원 자체를 생명공학 관련 기술로 제작·배양·증식하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="141" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생물농약·생물방제제품 제조업</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병해충 방제 또는 농작물 생리기능 조절에 사용하는 농약·방제제품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물 또는 생명공학 관련 기술·생물공정을 유효성분이나 방제기능에 직접 이용하여 제조하는 산업활동을 말한다. 살아 있는 미생물 또는 자연계 생성 화합물을 유효성분으로 하는 천연식물보호제도 이러한 생물자원과 연결되고 생명공학 관련 기술·생물공정의 직접 기여가 함께 확인되면 포함한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="66" customHeight="1">
+          <t xml:space="preserve">그린바이오 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 작물 생육·활력·스트레스 저항성 또는 재배환경을 개선하면서도, 병해충 방제·농작물 생리기능 조절에 사용하는 농약·방제제품이나 식물 영양 공급·재배 보조·토양개량에 사용하는 비료에는 해당하지 않는 생물촉진제·생물제제를 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="51" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 제품 제조업</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 사료 제조업</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동물의 영양·건강유지·성장에 필요한 단미사료·배합사료 중, 그린바이오 미생물·곤충·천연물 또는 생명공학 관련 발효·효소·생물전환 공정이 영양·기능·안전성에 실질적으로 기여하도록 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="51" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -666,31 +666,31 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">312</t>
+          <t xml:space="preserve">322</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 비료 제조업</t>
+          <t xml:space="preserve">그린바이오 사료첨가제 제조업</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">미생물·식물·해조류 등 그린바이오 생물자원 또는 발효·효소처리·생물전환 등의 생물공정을 이용하여 식물에 양분을 공급하거나 토양의 물리적·화학적·생물학적 특성을 개선하는 비료를 제조하는 산업활동을 말한다. 유용 미생물, 미생물 배양물·대사산물, 발효 아미노산·유기산 및 생물전환 양분 소재를 이용한 비료를 포함한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="66" customHeight="1">
+          <t xml:space="preserve">사료의 품질저하를 방지하거나 효용을 높이기 위해 첨가하는 보조사료 중, 생명공학 관련 기술·생물공정으로 생산한 생균제·효소제·아미노산·발효대사산물 등을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="111" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -703,27 +703,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 작물재배용 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">319</t>
+          <t xml:space="preserve">331</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 작물재배용 제품 제조업</t>
+          <t xml:space="preserve">그린바이오 식품원료·첨가물 제조업</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 작물 생육·활력·스트레스 저항성 또는 재배환경을 개선하면서도, 병해충 방제·농작물 생리기능 조절에 사용하는 농약·방제제품이나 식물 영양 공급·재배 보조·토양개량에 사용하는 비료에는 해당하지 않는 생물촉진제·생물제제를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">식품의 제조에 투입되는 원재료·중간생산물과, 식품을 제조·가공·조리 또는 보존하는 과정에서 감미·착색·표백·산화방지 등의 기술적 효과를 내기 위해 소량 사용하는 첨가물 및 발효·가공보조용 효소로서, 그린바이오 미생물·곤충·천연물 등 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 제조하는 산업활동을 말한다. 최종식품에 배합되어 그 구성 성분을 이루도록 분말·액상 등 별도 형태로 가공한 원료·중간소재와, 기술적 효과를 목적으로 소량 사용하는 첨가물·효소를 함께 포함한다. 두 갈래는 배합목적과 사용량으로 구분한다.</t>
         </is>
       </c>
     </row>
@@ -740,31 +740,31 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">321</t>
+          <t xml:space="preserve">332</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 사료 제조업</t>
+          <t xml:space="preserve">그린바이오 발효식품 제조업</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물의 영양·건강유지·성장에 필요한 단미사료·배합사료 중, 그린바이오 미생물·곤충·천연물 또는 생명공학 관련 발효·효소·생물전환 공정이 영양·기능·안전성에 실질적으로 기여하도록 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="51" customHeight="1">
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 특정 미생물·스타터와 문서화된 생명공학 관련 제어발효공정이 품질·기능에 실질적으로 기여하도록 식품·음료 완제품을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="126" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -777,31 +777,31 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 사료·사료첨가제 제조업</t>
+          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">333</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 사료첨가제 제조업</t>
+          <t xml:space="preserve">그린바이오 건강기능식품 제조업</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">사료의 품질저하를 방지하거나 효용을 높이기 위해 첨가하는 보조사료 중, 생명공학 관련 기술·생물공정으로 생산한 생균제·효소제·아미노산·발효대사산물 등을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="111" customHeight="1">
+          <t xml:space="preserve">인체에 유용한 기능성을 가진 원료나 성분을 사용하여 제조·가공한 식품으로서 「건강기능식품에 관한 법률」에 따라 건강기능식품으로 인정받은 완제품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고, 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="156" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -824,21 +824,21 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">331</t>
+          <t xml:space="preserve">334</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품원료·첨가물 제조업</t>
+          <t xml:space="preserve">그린바이오 특수영양·특수의료용도식품 제조업</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품의 제조에 투입되는 원재료·중간생산물과, 식품을 제조·가공·조리 또는 보존하는 과정에서 감미·착색·표백·산화방지 등의 기술적 효과를 내기 위해 소량 사용하는 첨가물 및 발효·가공보조용 효소로서, 그린바이오 미생물·곤충·천연물 등 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 제조하는 산업활동을 말한다. 최종식품에 배합되어 그 구성 성분을 이루도록 분말·액상 등 별도 형태로 가공한 원료·중간소재와, 기술적 효과를 목적으로 소량 사용하는 첨가물·효소를 함께 포함한다. 두 갈래는 배합목적과 사용량으로 구분한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="51" customHeight="1">
+          <t xml:space="preserve">영·유아, 비만자 또는 임산·수유부 등 특별한 영양관리가 필요한 특정 대상을 위하여 식품과 영양성분을 배합하는 등의 방법으로 제조·가공한 조제유류·조제식·이유식·체중조절용 조제식품·임산수유부용 식품·고령자용 영양조제식품과, 정상적으로 섭취·소화·흡수 또는 대사할 수 있는 능력이 제한되거나 질병·수술 등의 임상적 상태로 인하여 일반인과 생리적으로 특별히 다른 영양요구량을 가진 사람에게 식사의 일부 또는 전부를 대신할 목적으로 경구 또는 경관급식을 통하여 공급하도록 제조·가공한 식품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="81" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -861,21 +861,21 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">332</t>
+          <t xml:space="preserve">335</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물활용·발효식품 제조업</t>
+          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 특정 미생물·스타터와 문서화된 생명공학 관련 제어발효공정이 품질·기능에 실질적으로 기여하도록 식품·음료 완제품을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="126" customHeight="1">
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물에 세포배양·정밀발효·생물전환 등 생명공학 관련 기술을 직접 적용하여 축산물 등을 대체하는 식품 완제품을 제조하는 산업활동을 말한다. 배양식품의 원천 세포가 위 관련 분야의 생물체에서 유래함을 확인할 수 있어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="96" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -898,21 +898,21 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">333</t>
+          <t xml:space="preserve">339</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 건강기능성식품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 식품 제조업</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">인체에 유용한 기능성을 가진 원료·성분으로 제조한 식품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고, 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 건강기능식품·특수영양·특수의료용도 식용 완제품을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="36" customHeight="1">
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정이 제품의 특성이나 제조공정에 직접 기여하는 식용 완제품으로서, 발효식품, 건강기능식품, 특수영양·특수의료용도식품, 대체식품의 어느 것에도 해당하지 않는 것을 제조하는 산업활동을 말한다. 곤충을 원료로 한 스낵·바 등 식용 곤충 완제품이 대표적이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -925,31 +925,31 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 식품원료·식품 제조업</t>
+          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">334</t>
+          <t xml:space="preserve">341</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 대체식품 제조업</t>
+          <t xml:space="preserve">동물용 백신 및 기타 예방·치료용 생물학적 제제 제조업</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원에 세포배양·정밀발효·생물전환 등 생명공학 관련 기술을 직접 적용하여 축산물 등을 대체하는 식품 완제품을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="66" customHeight="1">
+          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생물체·세포·재조합기술 등 생명공학 관련 기술을 이용하여 동물 질병의 예방·치료 등을 위한 백신·항체·단백질·세포 기반 생물학적 제제를 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="81" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -972,21 +972,21 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">341</t>
+          <t xml:space="preserve">349</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물용 백신·생물학적 제제 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생물체·세포·재조합기술 등 생명공학 관련 기술을 이용하여 동물 질병의 예방·치료 등을 위한 백신·항체·단백질·세포 기반 생물학적 제제를 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="81" customHeight="1">
+          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제 또는 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 동물용체외진단의료기기와 기구·기계·장치는 포함하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="111" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -999,31 +999,31 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">349</t>
+          <t xml:space="preserve">391</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">기타 그린바이오 동물용 의약품 제조업</t>
+          <t xml:space="preserve">그린바이오 비식용 중간소재 제조업</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제 또는 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 동물용체외진단의료기기와 기구·기계·장치는 포함하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="111" customHeight="1">
+          <t xml:space="preserve">농업·식품·사료·동물용 의약품·비식용 소재 분야에 이용되는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 농업에 실제적이거나 잠재적인 가치가 있는 미생물에 생명공학 관련 기술·생물공정을 직접 적용하여 비식용·비사료용 추출물·오일·단백질·대사산물·효소 등 중간소재를 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="81" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -1046,21 +1046,21 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">391</t>
+          <t xml:space="preserve">392</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 천연물·곤충·미생물 유래 소재 제조업</t>
+          <t xml:space="preserve">그린바이오 향장·생활제품 제조업</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업·식품·사료·동물용 의약품·비식용 소재 분야에 이용되는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 농업에 실제적이거나 잠재적인 가치가 있는 미생물에 생명공학 관련 기술·생물공정을 직접 적용하여 비식용·비사료용 추출물·오일·단백질·대사산물·효소 등 중간소재를 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="81" customHeight="1">
+          <t xml:space="preserve">인체를 청결·미화하여 매력을 더하고 용모를 밝게 변화시키거나 피부·모발의 건강을 유지·증진하기 위해 바르거나 문지르거나 뿌리는 등의 방법으로 사용되고 인체에 대한 작용이 경미한 화장품과 비의약 생활제품 중, 그린바이오 생물자원과 생명공학 관련 기술·생물공정이 제품기능이나 제조공정에 직접 기여하도록 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="141" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -1083,243 +1083,243 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">392</t>
+          <t xml:space="preserve">399</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 향장·생활제품 제조업</t>
+          <t xml:space="preserve">기타 그린바이오 산업용 제품 제조업</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">인체를 청결·미화하여 매력을 더하고 용모를 밝게 변화시키거나 피부·모발의 건강을 유지·증진하기 위해 바르거나 문지르거나 뿌리는 등의 방법으로 사용되고 인체에 대한 작용이 경미한 화장품과 비의약 생활제품 중, 그린바이오 생물자원과 생명공학 관련 기술·생물공정이 제품기능이나 제조공정에 직접 기여하도록 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">증식용·재배용 씨앗·버섯 종균·묘목·포자·영양체 등의 종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 농업·식품·사료·소재 분야에서 산업적으로 이용되는 곤충, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업용 완제품으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 비식용 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="141" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 제품 제조업</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">399</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 산업용 제품 제조업</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">증식용·재배용 씨앗·버섯 종균·묘목·포자·영양체 등의 종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 농업·식품·사료·소재 분야에서 산업적으로 이용되는 곤충, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업소재·제품으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 천연물·곤충·미생물 유래 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="81" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">41</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 도매업</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용하여 개발·생산했거나 그린바이오 제조공정의 성분·품질규격에 따라 계약 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등 타사의 생물자원을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 사업자·기관에 재판매하며 해당 품목·매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="81" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">410</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 소매업자·산업사용자·기관 등 사업자에게 재판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 중간소재, 향장·생활제품과 산업용 제품이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="141" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도매업</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 소재·제품 도매업</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 미생물·곤충·천연물 등 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 타사가 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 소재, 향장·생활제품 및 산업용 소재·제품을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 사업자·기관에 재판매하며 해당 품목·매출을 분리하는 산업활동을 말한다.</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 소매업</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">420</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원·제품 소매업</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 본질적으로 변형하지 않고 일반소비자·최종 수요자에게 전문점·전자상거래 등으로 판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 향장·생활제품과 산업용 제품이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="51" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 연구개발 서비스업</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 생물자원 연구개발 서비스업</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 품종·종자·농업 미생물·균주·세포·곤충 등 생물자원의 탐색·육종·설계·개발 결과를 제공하고 해당 계약·매출을 분리하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="81" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 소매업</t>
+          <t xml:space="preserve">그린바이오 연구개발 서비스업</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">421</t>
+          <t xml:space="preserve">512</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원 소매업</t>
+          <t xml:space="preserve">그린바이오 제품·공정 연구개발 서비스업</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용하여 개발·생산했거나 그린바이오 제조공정의 성분·품질규격에 따라 계약 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등 타사의 생물자원을 본질적으로 변형하지 않고 일반소비자·최종 수요자에게 전문적으로 판매하며 해당 품목·매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="81" customHeight="1">
+          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 미생물·곤충·천연물 등 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 중간소재, 향장·생활제품과 그 배양·발효·추출·제조공정의 연구·설계·개발 결과를 제공하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="96" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 도소매업</t>
+          <t xml:space="preserve">그린바이오 관련 서비스업</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·제품 소매업</t>
+          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">422</t>
+          <t xml:space="preserve">520</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 소재·제품 소매업</t>
+          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 미생물·곤충·천연물 등 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 타사가 제조한 작물재배용 제품, 사료·사료첨가제, 식품·동물용 바이오의약품·향장품·생활제품 등을 본질적으로 변형하지 않고 전문점·전자상거래 등으로 일반소비자·최종 수요자에게 판매하며 해당 품목·매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="51" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충, 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품과 그 연구·생산·제조공정에 특화된 생물자원·품종·유전체·표현형·성분·공정 데이터베이스와 정보, 데이터 처리·해석 도구, 전문 소프트웨어 또는 디지털 플랫폼을 구축·운영하여 외부 이용자에게 지속적으로 제공하는 산업활동을 말한다. 이용대상·계약·매출을 일반 정보서비스와 분리할 수 있어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="96" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">그린바이오 관련 서비스업</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 연구개발 서비스업</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">511</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 생물자원 연구개발 서비스업</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 품종·종자·농업 미생물·균주·세포·곤충 등 생물자원의 탐색·육종·설계·개발 결과를 제공하고 해당 계약·매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="81" customHeight="1">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 교육 서비스업</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">530</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그린바이오 교육 서비스업</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수수료 또는 계약에 따라 외부 이용자에게 종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충, 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품에 적용되는 생명공학 관련 기술과 그 생산·제조공정의 육종·배양·발효·분석·제조·장비운영 실무, 그리고 해당 재화의 품질·안전·인허가·인증·지식재산·창업·수출에 관한 전문 교육·실습·훈련을 조직적으로 제공하고 관련 교육매출을 분리하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="51" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 연구개발 서비스업</t>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">512</t>
+          <t xml:space="preserve">541</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 소재·제품·공정 연구개발 서비스업</t>
+          <t xml:space="preserve">그린바이오 시험·분석 서비스업</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 미생물·곤충·천연물 등 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 소재, 향장·생활제품과 그 배양·발효·추출·제조공정의 연구·설계·개발 결과를 제공하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">수수료 또는 계약에 따라 그린바이오 생물자원·소재·제품의 효능·독성·안전성·환경·생물 위해성, 품질·성분·함량·물성·순도·오염 또는 유전체·전사체·단백체·대사체·세포·표현형을 시험·분석·평가하고 결과를 제공하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -1369,31 +1369,31 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">520</t>
+          <t xml:space="preserve">542</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 정보·데이터 서비스업</t>
+          <t xml:space="preserve">그린바이오 검사·인증 서비스업</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원·품종·유전체·표현형·성분·공정에 특화된 데이터베이스·정보, 데이터 처리·해석 도구, 소프트웨어 또는 디지털 플랫폼을 구축·운영하여 외부 이용자에게 지속적으로 제공하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="51" customHeight="1">
+          <t xml:space="preserve">수수료 또는 계약에 따라 그린바이오 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 제품·공정·시설을 정해진 기준으로 검사·검증·심사하고 인증서·성적서 등 판정 결과를 제공하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="126" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -1406,220 +1406,62 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 교육 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 관련 서비스업</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">531</t>
+          <t xml:space="preserve">590</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 기술·생산 교육 서비스업</t>
+          <t xml:space="preserve">기타 그린바이오 관련 서비스업</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 이용자에게 그린바이오 분야의 육종·배양·발효·분석·제조·장비운영 실무교육을 조직적으로 제공하고 관련 교육매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="66" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 교육 서비스업</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 품질·규제·사업화 교육 서비스업</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 이용자에게 그린바이오 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 제품의 품질·안전·인허가·인증·지식재산·창업·수출 전문교육을 제공하고 관련 교육매출을 분리하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="51" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 시험·분석·평가 서비스업</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 그린바이오 생물자원·소재·제품의 효능·독성·안전성·환경·생물 위해성, 품질·성분·함량·물성·순도·오염 또는 유전체·전사체·단백체·대사체·세포·표현형을 시험·분석·평가하고 결과를 제공하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="51" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 시험·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">542</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 검사·검증·인증 서비스업</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 그린바이오 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 제품·공정·시설을 정해진 기준으로 검사·검증·심사하고 인증서·성적서 등 판정 결과를 제공하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="126" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타 그린바이오 관련 서비스업</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
           <t xml:space="preserve">수수료 또는 계약에 따라 그린바이오 생물자원이나 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하는 재화의 사업화와 생산을 지원하는 서비스로서 달리 분류되지 않는 것을 외부 고객에게 제공하고 관련 계약·매출을 분리하는 산업활동을 말한다. 인허가·등록·규제 대응과 품질·안전·인증체계 구축을 위한 전문 자문·대행, 특정 기술·제품의 기술이전·지식재산·창업·투자유치·수출·시장진입 지원, 연구·생산·제조·시험분석에 사용하는 전용·주사용·특화 시설·장비의 임대·공동활용·설치 후 유지관리·수리·검증·교정, 생물학적 품질·안전·저온·추적성이 요구되는 전문 물류·보관과 시설·공정 운영지원을 포함한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="30">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="A15:A28"/>
-    <mergeCell ref="B15:B28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="B33:B40"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="A12:A27"/>
+    <mergeCell ref="B12:B27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B30:B36"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/그린바이오산업_특수분류표.xlsx
+++ b/그린바이오산업_특수분류표.xlsx
@@ -279,7 +279,7 @@
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조에 전용되거나 주로 사용되도록 특화된 기자재를 직접 제조하는 산업활동을 말한다. 배지·배양기질·시약·효소·완충용액·시약키트·유전자 벡터·담체·공정재 등 소모성 자재, 유전·세포·생물정보 또는 성분·품질·안전을 시험·측정·분석하는 연구·분석장비와 그 전용 부품, 배양·발효·분리·정제·건조·제형 장비와 생물자원의 증식·사육·재배 환경제어 장비 등 생산·공정장비를 포함한다. 자체 제조한 기자재의 판매는 이 산업활동에 포함한다.</t>
+          <t xml:space="preserve">생명공학 관련 기술이 적용되는 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품의 연구·생산·제조에 전용되거나 주로 사용되도록 특화된 기자재를 직접 제조하는 산업활동을 말한다. 배지·배양기질·시약·효소·완충용액·시약키트·유전자 벡터·담체·공정재 등 소모성 자재, 유전·세포·생물정보 또는 성분·품질·안전을 시험·측정·분석하는 연구·분석장비와 그 전용 부품, 배양·발효·분리·정제·건조·제형 장비와 생물자원의 증식·사육·재배 환경제어 장비 등 생산·공정장비를 포함한다.</t>
         </is>
       </c>
     </row>
@@ -353,7 +353,7 @@
       </c>
       <c r="G7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">생명공학 관련 육종·유전체·선발·편집 기술을 적용하여 식물 품종을 개발하거나 해당 품종의 원원종·원종·모본·부본·보급종·판매용 종자·묘목·묘종·조직배양묘를 생산·증식하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">생명공학 관련 육종·유전체·선발 기술을 적용하여 식물 품종을 개발하거나 해당 품종의 원원종·원종·모본·부본·보급종·판매용 종자·묘목·묘종·조직배양묘와 「종자산업법」상 종자에 포함되는 버섯 종균을 생산·증식하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -468,7 +468,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="81" customHeight="1">
+    <row r="11" ht="66" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -501,11 +501,11 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 생물기원 천연물의 원천이 되는 육상·해양 생물체에서 유래한 세포·조직·세포주 자원 자체를 생명공학 관련 기술로 제작·배양·증식하여 그린바이오 연구·생산에 공급하는 산업활동을 말한다. 자원의 원천 생물체가 위 관련 분야에 해당함을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="141" customHeight="1">
+          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 생물기원 천연물의 원천이 되는 육상·해양 생물체에서 유래한 세포·조직·세포주 자원 자체를 생명공학 관련 기술로 제작·배양·증식하여 그린바이오 연구·생산에 공급하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="51" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -538,7 +538,7 @@
       </c>
       <c r="G12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">병해충 방제 또는 농작물 생리기능 조절에 사용하는 농약·방제제품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물 또는 생명공학 관련 기술·생물공정을 유효성분이나 방제기능에 직접 이용하여 제조하는 산업활동을 말한다. 살아 있는 미생물 또는 자연계 생성 화합물을 유효성분으로 하는 천연식물보호제도 이러한 생물자원과 연결되고 생명공학 관련 기술·생물공정의 직접 기여가 함께 확인되면 포함한다.</t>
+          <t xml:space="preserve">병해충 방제 또는 농작물 생리기능 조절에 사용하는 농약·방제제품 중, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정을 유효성분이나 방제기능에 직접 이용하여 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="66" customHeight="1">
+    <row r="14" ht="51" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -612,7 +612,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 작물 생육·활력·스트레스 저항성 또는 재배환경을 개선하면서도, 병해충 방제·농작물 생리기능 조절에 사용하는 농약·방제제품이나 식물 영양 공급·재배 보조·토양개량에 사용하는 비료에는 해당하지 않는 생물촉진제·생물제제를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 작물의 생육·활력·스트레스 저항성이나 재배환경을 개선하는 제품 중 달리 분류되지 않는 것을 제조하는 산업활동을 말한다. 생물촉진제·생물제제 등이 이에 해당한다.</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">동물의 영양·건강유지·성장에 필요한 단미사료·배합사료 중, 그린바이오 미생물·곤충·천연물 또는 생명공학 관련 발효·효소·생물전환 공정이 영양·기능·안전성에 실질적으로 기여하도록 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">동물의 영양·건강유지·성장에 필요한 단미사료·배합사료 중, 그린바이오 생물자원이나 발효·효소·생물전환 등 생명공학 관련 생물공정이 영양·기능·안전성에 실질적으로 기여하는 것을 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">식품의 제조에 투입되는 원재료·중간생산물과, 식품을 제조·가공·조리 또는 보존하는 과정에서 감미·착색·표백·산화방지 등의 기술적 효과를 내기 위해 소량 사용하는 첨가물 및 발효·가공보조용 효소로서, 그린바이오 미생물·곤충·천연물 등 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 제조하는 산업활동을 말한다. 최종식품에 배합되어 그 구성 성분을 이루도록 분말·액상 등 별도 형태로 가공한 원료·중간소재와, 기술적 효과를 목적으로 소량 사용하는 첨가물·효소를 함께 포함한다. 두 갈래는 배합목적과 사용량으로 구분한다.</t>
+          <t xml:space="preserve">식품의 제조에 투입되는 원재료·중간생산물과, 식품을 제조·가공·조리 또는 보존하는 과정에서 감미·착색·표백·산화방지 등의 기술적 효과를 내기 위해 소량 사용하는 첨가물 및 발효·가공보조용 효소로서, 그린바이오 미생물·곤충·천연물 등 생물자원 또는 생명공학 관련 기술·생물공정을 직접 이용하여 제조하는 산업활동을 말한다. 최종식품에 배합되어 그 구성 성분을 이루도록 분말·액상 등 별도 형태로 가공한 원료·중간소재와, 기술적 효과를 목적으로 소량 사용하는 첨가물·효소를 함께 포함한다.</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="126" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -797,11 +797,11 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">인체에 유용한 기능성을 가진 원료나 성분을 사용하여 제조·가공한 식품으로서 「건강기능식품에 관한 법률」에 따라 건강기능식품으로 인정받은 완제품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고, 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="156" customHeight="1">
+          <t xml:space="preserve">인체에 유용한 기능성을 가진 원료나 성분을 사용하여 제조·가공한 식품으로서 「건강기능식품에 관한 법률」에 따라 건강기능식품으로 인정받은 완제품 중, 그린바이오 생물자원을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="126" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -834,11 +834,11 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">영·유아, 비만자 또는 임산·수유부 등 특별한 영양관리가 필요한 특정 대상을 위하여 식품과 영양성분을 배합하는 등의 방법으로 제조·가공한 조제유류·조제식·이유식·체중조절용 조제식품·임산수유부용 식품·고령자용 영양조제식품과, 정상적으로 섭취·소화·흡수 또는 대사할 수 있는 능력이 제한되거나 질병·수술 등의 임상적 상태로 인하여 일반인과 생리적으로 특별히 다른 영양요구량을 가진 사람에게 식사의 일부 또는 전부를 대신할 목적으로 경구 또는 경관급식을 통하여 공급하도록 제조·가공한 식품 중, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="81" customHeight="1">
+          <t xml:space="preserve">영·유아, 비만자 또는 임산·수유부 등 특별한 영양관리가 필요한 특정 대상을 위하여 식품과 영양성분을 배합하는 등의 방법으로 제조·가공한 조제유류·조제식·이유식·체중조절용 조제식품·임산수유부용 식품·고령자용 영양조제식품과, 정상적으로 섭취·소화·흡수 또는 대사할 수 있는 능력이 제한되거나 질병·수술 등의 임상적 상태로 인하여 일반인과 생리적으로 특별히 다른 영양요구량을 가진 사람에게 식사의 일부 또는 전부를 대신할 목적으로 경구 또는 경관급식을 통하여 공급하도록 제조·가공한 식품 중, 그린바이오 생물자원을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정의 직접 기여가 함께 입증된 것을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -871,11 +871,11 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물에 세포배양·정밀발효·생물전환 등 생명공학 관련 기술을 직접 적용하여 축산물 등을 대체하는 식품 완제품을 제조하는 산업활동을 말한다. 배양식품의 원천 세포가 위 관련 분야의 생물체에서 유래함을 확인할 수 있어야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="96" customHeight="1">
+          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물에 세포배양·정밀발효·생물전환 등 생명공학 관련 기술을 직접 적용하여 축산물 등을 대체하는 식품 완제품을 제조하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="81" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -908,11 +908,11 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충 또는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정이 제품의 특성이나 제조공정에 직접 기여하는 식용 완제품으로서, 발효식품, 건강기능식품, 특수영양·특수의료용도식품, 대체식품의 어느 것에도 해당하지 않는 것을 제조하는 산업활동을 말한다. 곤충을 원료로 한 스낵·바 등 식용 곤충 완제품이 대표적이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="66" customHeight="1">
+          <t xml:space="preserve">그린바이오 생물자원을 원료·성분으로 이용하고 생명공학 관련 기술·생물공정이 제품의 특성이나 제조공정에 직접 기여하는 식용 완제품으로서, 발효식품, 건강기능식품, 특수영양·특수의료용도식품, 대체식품의 어느 것에도 해당하지 않는 것을 제조하는 산업활동을 말한다. 곤충을 원료로 한 스낵·바 등 식용 곤충 완제품이 대표적이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="51" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -945,7 +945,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생물체·세포·재조합기술 등 생명공학 관련 기술을 이용하여 동물 질병의 예방·치료 등을 위한 백신·항체·단백질·세포 기반 생물학적 제제를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">「약사법」이 정한 의약품 중 동물용으로만 사용하는 것으로서, 생물체·세포·재조합기술 등 생명공학 관련 기술을 이용하여 동물 질병의 예방·치료 등에 사용하는 백신·항체·단백질·세포 기반 생물학적 제제를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -982,11 +982,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」이 정한 의약품, 즉 기구·기계 또는 장치가 아닌 물품으로서 동물용으로만 사용하는 것 중 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제 또는 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 동물용체외진단의료기기와 기구·기계·장치는 포함하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="111" customHeight="1">
+          <t xml:space="preserve">「약사법」이 정한 의약품 중 동물용으로만 사용하는 것으로서, 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제나 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 진단액·진단항원 등 진단용 생물학적 제제가 대표적이다. 동물용체외진단의료기기와 기구·기계·장치는 포함하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">농업·식품·사료·동물용 의약품·비식용 소재 분야에 이용되는 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 분류학상 곤충강에 속하는 동물과 거미류·지네류 등 「곤충산업의 육성 및 지원에 관한 법률」이 곤충으로 정하는 무척추동물(사슴벌레·동애등에·뒤영벌·천적 응애 등) 중 농업·식품·사료·소재 분야에서 산업적으로 이용되는 것 또는 농업에 실제적이거나 잠재적인 가치가 있는 미생물에 생명공학 관련 기술·생물공정을 직접 적용하여 비식용·비사료용 추출물·오일·단백질·대사산물·효소 등 중간소재를 제조하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">그린바이오 생물자원에 생명공학 관련 기술·생물공정을 직접 적용하여 비식용·비사료용 추출물·오일·단백질·대사산물·효소 등 중간소재를 제조하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="141" customHeight="1">
+    <row r="27" ht="96" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">증식용·재배용 씨앗·버섯 종균·묘목·포자·영양체 등의 종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 농업·식품·사료·소재 분야에서 산업적으로 이용되는 곤충, 육상·해양 생물체와 그 세포·조직배양 산물 등 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업용 완제품으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 비식용 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
+          <t xml:space="preserve">그린바이오 생물자원과 식품 제조용 가공 원재료·중간생산물, 동물용 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업용 완제품으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 비식용 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 소매업자·산업사용자·기관 등 사업자에게 재판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 중간소재, 향장·생활제품과 산업용 제품이다.</t>
+          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 소매업자·산업사용자·기관 등 사업자에게 재판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 중간소재, 향장·생활제품과 산업용 제품이다.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 본질적으로 변형하지 않고 일반소비자·최종 수요자에게 전문점·전자상거래 등으로 판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·편집·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 향장·생활제품과 산업용 제품이다.</t>
+          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 본질적으로 변형하지 않고 일반소비자·최종 수요자에게 전문점·전자상거래 등으로 판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 향장·생활제품과 산업용 제품이다.</t>
         </is>
       </c>
     </row>

--- a/그린바이오산업_특수분류표.xlsx
+++ b/그린바이오산업_특수분류표.xlsx
@@ -202,13 +202,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대분류 5 · 중분류 17 · 소분류 32   |   작업안 · 국가데이터처 승인 전   |   정의 원문은 소분류 정의서</t>
-        </is>
-      </c>
-    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -949,7 +942,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="81" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
@@ -982,7 +975,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">「약사법」이 정한 의약품 중 동물용으로만 사용하는 것으로서, 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제나 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 진단액·진단항원 등 진단용 생물학적 제제가 대표적이다. 동물용체외진단의료기기와 기구·기계·장치는 포함하지 않는다.</t>
+          <t xml:space="preserve">「약사법」이 정한 의약품 중 동물용으로만 사용하는 것으로서, 생명공학 관련 기술을 이용하여 동물에 직접 투여해 질병을 진단하는 생물학적 제제나 동물용 백신·항체·단백질·세포 기반 생물학적 제제에 해당하지 않는 그 밖의 바이오의약품을 제조하는 산업활동을 말한다. 진단액·진단항원 등 진단용 생물학적 제제가 대표적이다.</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1086,11 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">그린바이오 생물자원과 식품 제조용 가공 원재료·중간생산물, 동물용 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업용 완제품으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 비식용 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="141" customHeight="1">
+          <t xml:space="preserve">그린바이오 생물자원과 식품 제조용 가공 원재료·중간생산물, 동물용 의약품의 농업적 생산·가공·활용에 직접 사용되거나 그 과정에서 산출되는 비식용·비사료용 산업용 완제품 중 달리 분류되지 않는 것으로서, 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하고 농업 전후방 부가가치가 확인되는 것을 제조하는 산업활동을 말한다. 다만 작물재배용 제품, 동물용 의약품, 비식용 중간소재 및 향장·생활제품은 포함하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -1130,11 +1123,11 @@
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 자기 계정으로 구입하여, 본질적으로 변형하지 않고 소매업자·산업사용자·기관 등 사업자에게 재판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물·기능성 식품소재용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 비식용 중간소재, 향장·생활제품과 산업용 제품이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="141" customHeight="1">
+          <t xml:space="preserve">그린바이오 생물자원·소재·제품을 구입하여 소매업자·산업사용자·기관 등에 재판매하는 산업활동을 말한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
@@ -1167,7 +1160,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">타사가 생산·제조한 그린바이오 생물자원·소재·제품을 본질적으로 변형하지 않고 일반소비자·최종 수요자에게 전문점·전자상거래 등으로 판매하며 해당 품목·매출을 일반 상품과 분리하는 산업활동을 말한다. 취급 대상은 생명공학 관련 육종·유전체·선발·배양·증식 기술을 적용해 개발·생산했거나 확인된 그린바이오 제조공정의 성분·품질규격 또는 계약에 따라 생산한 종자·종묘·미생물·종균·균주·세포·곤충·천연물 원료용 식물 등의 생물자원과, 그린바이오 생물자원 또는 생명공학 관련 기술·생물공정이 제품기능 또는 제조공정에 직접 기여하도록 제조한 작물재배용 제품, 사료·사료첨가제, 식품원료·식품, 동물용 바이오의약품, 향장·생활제품과 산업용 제품이다.</t>
+          <t xml:space="preserve">그린바이오 생물자원·소재·제품을 일반소비자 또는 최종 수요자에게 판매하는 산업활동을 말한다. 전문점·전자상거래를 통한 판매를 포함한다.</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1197,7 @@
       </c>
       <c r="G30" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 품종·종자·농업 미생물·균주·세포·곤충 등 생물자원의 탐색·육종·설계·개발 결과를 제공하고 해당 계약·매출을 분리하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">수수료 또는 계약에 따라 외부 고객에게 그린바이오 품종·종자·농업 미생물·균주·세포·곤충 등 생물자원의 탐색·육종·설계·개발 결과를 제공하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="96" customHeight="1">
+    <row r="32" ht="126" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -1278,11 +1271,11 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충, 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품과 그 연구·생산·제조공정에 특화된 생물자원·품종·유전체·표현형·성분·공정 데이터베이스와 정보, 데이터 처리·해석 도구, 전문 소프트웨어 또는 디지털 플랫폼을 구축·운영하여 외부 이용자에게 지속적으로 제공하는 산업활동을 말한다. 이용대상·계약·매출을 일반 정보서비스와 분리할 수 있어야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="96" customHeight="1">
+          <t xml:space="preserve">종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충, 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품과 그 연구·생산·제조공정에 특화된 생물자원·품종·유전체·표현형·성분·공정 데이터베이스와 정보, 데이터 처리·해석 도구, 전문 소프트웨어 또는 디지털 플랫폼을 개발·구축·운영하여 외부 이용자에게 지속적으로 제공하는 산업활동을 말한다. 그린바이오에 특화된 소프트웨어·플랫폼의 개발과 그 운영·유지·고도화 서비스를 포함한다. 이용대상·계약·매출을 일반 정보서비스와 분리할 수 있어야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="51" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
@@ -1315,7 +1308,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">수수료 또는 계약에 따라 외부 이용자에게 종자, 농업에 실제적이거나 잠재적인 가치가 있는 미생물, 산업적으로 이용되는 곤충, 생물기원 천연물, 식품 제조용 가공 원재료·중간생산물 또는 동물용으로만 사용하는 의약품에 적용되는 생명공학 관련 기술과 그 생산·제조공정의 육종·배양·발효·분석·제조·장비운영 실무, 그리고 해당 재화의 품질·안전·인허가·인증·지식재산·창업·수출에 관한 전문 교육·실습·훈련을 조직적으로 제공하고 관련 교육매출을 분리하는 산업활동을 말한다.</t>
+          <t xml:space="preserve">외부 이용자를 대상으로 종자·미생물·곤충·천연물·식품 제조용 원재료·동물용 의약품에 적용되는 생명공학 관련 기술과 그 생산·제조공정, 품질·안전·규제와 사업화에 관한 전문 교육·실습·훈련을 제공하는 산업활동을 말한다.</t>
         </is>
       </c>
     </row>
@@ -1431,9 +1424,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C7:C8"/>
